--- a/Green-Holloway_Ex3A_tables.xlsx
+++ b/Green-Holloway_Ex3A_tables.xlsx
@@ -5,18 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\W2_Workshop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53BAC99B-9EE5-4DC8-9BA5-8CEC4C335738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0BD43C9-EC6E-4310-822E-547BCF87A9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22710" yWindow="6870" windowWidth="21045" windowHeight="13290" activeTab="3" xr2:uid="{54D012AC-9917-4171-A189-580612A27BF1}"/>
+    <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" xr2:uid="{54D012AC-9917-4171-A189-580612A27BF1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Events" sheetId="1" r:id="rId1"/>
-    <sheet name="Attendees" sheetId="2" r:id="rId2"/>
-    <sheet name="Registrations" sheetId="3" r:id="rId3"/>
+    <sheet name="Bookings" sheetId="1" r:id="rId1"/>
+    <sheet name="Owners" sheetId="2" r:id="rId2"/>
+    <sheet name="Dogs" sheetId="3" r:id="rId3"/>
     <sheet name="Locations" sheetId="4" r:id="rId4"/>
+    <sheet name="Walks" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t>event_name</t>
   </si>
@@ -50,9 +51,6 @@
     <t>description</t>
   </si>
   <si>
-    <t>attendee_id</t>
-  </si>
-  <si>
     <t>first_name</t>
   </si>
   <si>
@@ -65,18 +63,9 @@
     <t>phone</t>
   </si>
   <si>
-    <t xml:space="preserve">event_id </t>
-  </si>
-  <si>
     <t xml:space="preserve">location_id </t>
   </si>
   <si>
-    <t>registration_id</t>
-  </si>
-  <si>
-    <t>event_id</t>
-  </si>
-  <si>
     <t>registration_date</t>
   </si>
   <si>
@@ -95,7 +84,34 @@
     <t>city</t>
   </si>
   <si>
-    <t>state</t>
+    <t>Owner_id</t>
+  </si>
+  <si>
+    <t>Dogs_id</t>
+  </si>
+  <si>
+    <t>owner_id</t>
+  </si>
+  <si>
+    <t>park_name</t>
+  </si>
+  <si>
+    <t>walk_id</t>
+  </si>
+  <si>
+    <t>walk_date</t>
+  </si>
+  <si>
+    <t>duration_minutes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Booking_id </t>
+  </si>
+  <si>
+    <t>booking_id</t>
   </si>
 </sst>
 </file>
@@ -500,7 +516,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -509,7 +525,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -534,19 +550,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -560,6 +576,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
@@ -567,19 +584,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -596,24 +613,57 @@
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
         <v>17</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F427BEFA-91AC-4FE6-910A-2B0E77035F17}">
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Green-Holloway_Ex3A_tables.xlsx
+++ b/Green-Holloway_Ex3A_tables.xlsx
@@ -1,52 +1,168 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\W2_Workshop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C63381-75FC-4F0A-92E1-B6B545A75195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="10170" yWindow="4560" windowWidth="21045" windowHeight="13290" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Owners" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dogs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Walks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bookings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Owners" sheetId="1" r:id="rId1"/>
+    <sheet name="Dogs" sheetId="2" r:id="rId2"/>
+    <sheet name="Walks" sheetId="3" r:id="rId3"/>
+    <sheet name="Locations" sheetId="4" r:id="rId4"/>
+    <sheet name="Bookings" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="33">
+  <si>
+    <t>owner_id</t>
+  </si>
+  <si>
+    <t>first_name</t>
+  </si>
+  <si>
+    <t>last_name</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>dog_id</t>
+  </si>
+  <si>
+    <t>dog_name</t>
+  </si>
+  <si>
+    <t>breed</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>walk_id</t>
+  </si>
+  <si>
+    <t>walk_date</t>
+  </si>
+  <si>
+    <t>location_id</t>
+  </si>
+  <si>
+    <t>duration_minutes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>park_name</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>booking_id</t>
+  </si>
+  <si>
+    <t>booking_date</t>
+  </si>
+  <si>
+    <t>walk_status</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>Jdoe@yahoo.com</t>
+  </si>
+  <si>
+    <t>401-402-4003</t>
+  </si>
+  <si>
+    <t>Frisk</t>
+  </si>
+  <si>
+    <t>poodle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Happy dog </t>
+  </si>
+  <si>
+    <t>patterson park</t>
+  </si>
+  <si>
+    <t>0001 pk circle</t>
+  </si>
+  <si>
+    <t>baltimore</t>
+  </si>
+  <si>
+    <t>maryland</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ADD8E6"/>
-        <bgColor rgb="00ADD8E6"/>
+        <fgColor rgb="FFADD8E6"/>
+        <bgColor rgb="FFADD8E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0090EE90"/>
-        <bgColor rgb="0090EE90"/>
+        <fgColor rgb="FF90EE90"/>
+        <bgColor rgb="FF90EE90"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,86 +175,31 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -426,46 +487,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col min="1" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>owner_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>first_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>last_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>101</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{BB666B9B-4A57-40AD-A94A-4DB7E68E84FB}"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>202</v>
+      </c>
+      <c r="B2">
+        <v>101</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -473,47 +585,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col min="1" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>dog_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>owner_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>dog_name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>breed</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>303</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46045</v>
+      </c>
+      <c r="C2">
+        <v>404</v>
+      </c>
+      <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -521,47 +634,46 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col min="1" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>walk_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>walk_date</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>location_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>duration_minutes</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>404</v>
+      </c>
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -569,95 +681,46 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col min="1" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>location_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>park_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>city</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>booking_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>walk_id</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>dog_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>booking_date</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>walk_status</t>
-        </is>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>606</v>
+      </c>
+      <c r="B2">
+        <v>303</v>
+      </c>
+      <c r="C2">
+        <v>202</v>
+      </c>
+      <c r="D2" s="4">
+        <v>46045</v>
+      </c>
+      <c r="E2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
